--- a/CORREO DE TIENDAS.xlsx
+++ b/CORREO DE TIENDAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACBF7CF-AAB8-4090-9B16-3C2BE4C10C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A17ED1D-2D9C-4312-A30C-B69B007E8AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C23E9A61-2B91-457D-AE73-528FB7D973A8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>TIENDA</t>
   </si>
@@ -222,13 +222,19 @@
   </si>
   <si>
     <t>flepuntosurgdl@divec-flexi.com</t>
+  </si>
+  <si>
+    <t>LATITUD</t>
+  </si>
+  <si>
+    <t>LONGITUD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,12 +246,6 @@
       <b/>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -264,6 +264,17 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -292,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -315,77 +326,53 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -736,16 +723,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C1CFC4-A975-49BE-A816-07FE9F1D8EC5}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -758,284 +747,404 @@
       <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="8">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4">
+      <c r="E2" s="11">
+        <v>20.652626507572698</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-103.401443348291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="4">
+      <c r="E3" s="11">
+        <v>20.678839472311001</v>
+      </c>
+      <c r="F3" s="11">
+        <v>-103.394212134798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="11">
         <v>56</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
+      <c r="E4" s="11">
+        <v>20.524072981108599</v>
+      </c>
+      <c r="F4" s="11">
+        <v>-103.482387019459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
         <v>59</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="E5" s="11">
+        <v>21.882845507780502</v>
+      </c>
+      <c r="F5" s="11">
+        <v>-102.296172034755</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="11">
         <v>81</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="E6" s="11">
+        <v>20.674307905116201</v>
+      </c>
+      <c r="F6" s="11">
+        <v>-103.405113192469</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
         <v>98</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+      <c r="E7" s="11">
+        <v>20.651815487549701</v>
+      </c>
+      <c r="F7" s="11">
+        <v>-103.401610905963</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="11">
         <v>109</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="E8" s="11">
+        <v>20.677393112826099</v>
+      </c>
+      <c r="F8" s="11">
+        <v>-103.431479705962</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
         <v>119</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+      <c r="E9" s="11">
+        <v>21.926263241022301</v>
+      </c>
+      <c r="F9" s="11">
+        <v>-102.289603963589</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
         <v>121</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
+      <c r="E10" s="11">
+        <v>21.492111251467801</v>
+      </c>
+      <c r="F10" s="11">
+        <v>-104.866429705933</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
         <v>122</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="E11" s="11">
+        <v>20.712619995013998</v>
+      </c>
+      <c r="F11" s="11">
+        <v>-103.413691834796</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
         <v>124</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
+      <c r="E12" s="11">
+        <v>20.658675689765001</v>
+      </c>
+      <c r="F12" s="11">
+        <v>-105.23864551787</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
         <v>125</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
+      <c r="E13" s="11">
+        <v>19.105329229191</v>
+      </c>
+      <c r="F13" s="11">
+        <v>-104.332530406014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
         <v>131</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="4">
+      <c r="E14" s="11">
+        <v>20.647804614263201</v>
+      </c>
+      <c r="F14" s="11">
+        <v>-103.320665463635</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
         <v>133</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4">
+      <c r="E15" s="11">
+        <v>20.556943353994502</v>
+      </c>
+      <c r="F15" s="11">
+        <v>-103.46432516578901</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
         <v>143</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="10" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
+      <c r="E16" s="11">
+        <v>20.688986304952302</v>
+      </c>
+      <c r="F16" s="11">
+        <v>-103.29548744829</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
         <v>157</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="10" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="4">
+      <c r="E17" s="11">
+        <v>21.8802387797809</v>
+      </c>
+      <c r="F17" s="11">
+        <v>-102.260598905919</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
         <v>182</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="4">
+      <c r="E18" s="11">
+        <v>20.695691420802898</v>
+      </c>
+      <c r="F18" s="11">
+        <v>-103.376002405961</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
         <v>184</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="4">
+      <c r="E19" s="11">
+        <v>20.644063303062001</v>
+      </c>
+      <c r="F19" s="11">
+        <v>-103.41207424569799</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
         <v>186</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12"/>
+      <c r="E20" s="11">
+        <v>20.5694632021745</v>
+      </c>
+      <c r="F20" s="11">
+        <v>-103.453909763637</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D22">
